--- a/Excel BI Challenges/Power Query/392_PQ_Challenge.xlsx
+++ b/Excel BI Challenges/Power Query/392_PQ_Challenge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/29f448ec057303af/== Github Repos/Challenges/Excel BI Challenges/Power Query/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{4873A1D7-C550-4BA0-BE06-3B737FFDF286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8198295E-45B7-41FC-8DEA-DA5AD294AFDA}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{4873A1D7-C550-4BA0-BE06-3B737FFDF286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54397F90-F6AD-436A-A147-76A66AB90CFC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,9 +49,8 @@
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
+  <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -62,25 +61,11 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-  </valueMetadata>
 </metadata>
 </file>
 
@@ -108,8 +93,8 @@
 df_grouped = df.groupby("User_ID", as_index = False)["Page_Visited"].agg(
     Entry_Page = "first",
     Exit_Page = "last",
-    Unique_Pages_Visited = lambda x: len(set(x))
-    Full_Navigation_Path = .join(" &gt; ")
+    Unique_Pages_Visited = lambda x: len(set(x)),
+    Full_Navigation_Path = " &gt; ".join
 )
 df_grouped</code>
     </pythonScript>
@@ -581,70 +566,6 @@
 </queryTable>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>523f6e77d76248e28f160cf25dc6f3e2</v>
-    <v>invalid syntax. Perhaps you forgot a comma? (line 7)</v>
-    <v>SyntaxError</v>
-    <v>18</v>
-    <v>1</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_error">
-    <k n="correlationId" t="s"/>
-    <k n="errorMessage" t="s"/>
-    <k n="errorName" t="s"/>
-    <k n="errorType" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{96C0E280-BAE2-467C-A05E-2C442111BD13}" name="tblStart" displayName="tblStart" ref="A1:C22" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="4">
   <autoFilter ref="A1:C22" xr:uid="{96C0E280-BAE2-467C-A05E-2C442111BD13}"/>
@@ -1432,12 +1353,40 @@
       <c r="C16" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E16" t="e" cm="1" vm="1">
-        <f t="array" ref="E16">_xlfn._xlws.PY(0,1,A1:C22)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E16" t="str" cm="1">
+        <f t="array" ref="E16:I19">_xlfn._xlws.PY(0,0,A1:C22)</f>
+        <v>User_ID</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Entry_Page</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Exit_Page</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Unique_Pages_Visited</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Full_Navigation_Path</v>
+      </c>
+      <c r="K16" t="b" cm="1">
+        <f t="array" ref="K16:O19">_xlfn.ANCHORARRAY(E16)=E1:I4</f>
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>12</v>
       </c>
@@ -1447,8 +1396,38 @@
       <c r="C17" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E17" t="str">
+        <v>U1</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Home</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Profile</v>
+      </c>
+      <c r="H17">
+        <v>6</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Home &gt; Products &gt; Cart &gt; Checkout &gt; Confirmation &gt; Home &gt; Profile</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>15</v>
       </c>
@@ -1458,8 +1437,38 @@
       <c r="C18" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E18" t="str">
+        <v>U2</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Home</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Cart</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Home &gt; Blog &gt; Contact &gt; Home &gt; Products &gt; Cart</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>15</v>
       </c>
@@ -1469,8 +1478,38 @@
       <c r="C19" s="11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E19" t="str">
+        <v>U3</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Home</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Support</v>
+      </c>
+      <c r="H19">
+        <v>7</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Home &gt; About &gt; FAQ &gt; Home &gt; Products &gt; Cart &gt; Checkout &gt; Support</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>15</v>
       </c>
@@ -1481,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>15</v>
       </c>
@@ -1492,7 +1531,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>15</v>
       </c>
